--- a/xls/square_12_tri3_23.xlsx
+++ b/xls/square_12_tri3_23.xlsx
@@ -482,13 +482,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>-0.013992716731162699</v>
+        <v>-0.013992716449576165</v>
       </c>
       <c r="J23">
-        <v>-0.009166138955622542</v>
+        <v>-0.009166138773651947</v>
       </c>
       <c r="K23">
-        <v>2.908620081640672</v>
+        <v>2.908620074103792</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -517,13 +517,13 @@
         <v>3456</v>
       </c>
       <c r="I24">
-        <v>-0.0001063368897420603</v>
+        <v>-0.0001063368897509825</v>
       </c>
       <c r="J24">
-        <v>-8.326983384921092e-5</v>
+        <v>-8.326983385398526e-5</v>
       </c>
       <c r="K24">
-        <v>2.320858577813397</v>
+        <v>2.3208585776189166</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -552,13 +552,13 @@
         <v>3750</v>
       </c>
       <c r="I25">
-        <v>-0.0002859643896903882</v>
+        <v>-0.0002859643896059057</v>
       </c>
       <c r="J25">
-        <v>-0.00020478135079345534</v>
+        <v>-0.0002047813507354719</v>
       </c>
       <c r="K25">
-        <v>2.469166485178919</v>
+        <v>2.469166484974925</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -587,13 +587,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>-0.00011786648362884589</v>
+        <v>-0.00011786648361712612</v>
       </c>
       <c r="J26">
-        <v>-8.513189647768103e-5</v>
+        <v>-8.513189647276199e-5</v>
       </c>
       <c r="K26">
-        <v>2.286986508257883</v>
+        <v>2.286986508257642</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -622,13 +622,13 @@
         <v>4374</v>
       </c>
       <c r="I27">
-        <v>-0.00012038810144287932</v>
+        <v>-0.00012038810143950324</v>
       </c>
       <c r="J27">
-        <v>-8.997041452194885e-5</v>
+        <v>-8.997041452045383e-5</v>
       </c>
       <c r="K27">
-        <v>2.312040424850236</v>
+        <v>2.3120404250500086</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -657,13 +657,13 @@
         <v>4704</v>
       </c>
       <c r="I28">
-        <v>-0.00010716619139502258</v>
+        <v>-0.00010716619138137397</v>
       </c>
       <c r="J28">
-        <v>-8.03400879973143e-5</v>
+        <v>-8.03400879883444e-5</v>
       </c>
       <c r="K28">
-        <v>2.2905629960179708</v>
+        <v>2.2905629960528517</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -692,13 +692,13 @@
         <v>5046</v>
       </c>
       <c r="I29">
-        <v>-0.00011122733762106436</v>
+        <v>-0.00011122733760085653</v>
       </c>
       <c r="J29">
-        <v>-8.278662946793922e-5</v>
+        <v>-8.278662945530411e-5</v>
       </c>
       <c r="K29">
-        <v>2.293526951638249</v>
+        <v>2.293526951646369</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -727,13 +727,13 @@
         <v>5400</v>
       </c>
       <c r="I30">
-        <v>-0.00010302339537524512</v>
+        <v>-0.00010302339537259258</v>
       </c>
       <c r="J30">
-        <v>-7.894675737024334e-5</v>
+        <v>-7.894675736942351e-5</v>
       </c>
       <c r="K30">
-        <v>2.2960010263514765</v>
+        <v>2.296001026430135</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -762,13 +762,13 @@
         <v>5766</v>
       </c>
       <c r="I31">
-        <v>-8.64346353244977e-5</v>
+        <v>-8.643463532416012e-5</v>
       </c>
       <c r="J31">
-        <v>-6.692504538577568e-5</v>
+        <v>-6.692504538514876e-5</v>
       </c>
       <c r="K31">
-        <v>2.2666243592217556</v>
+        <v>2.266624359387928</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -797,13 +797,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>-0.00011516577303176033</v>
+        <v>-0.0001151657730105395</v>
       </c>
       <c r="J32">
-        <v>-8.194963676771527e-5</v>
+        <v>-8.194963675493552e-5</v>
       </c>
       <c r="K32">
-        <v>2.2708156122491707</v>
+        <v>2.2708156120135676</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_12_tri3_23.xlsx
+++ b/xls/square_12_tri3_23.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21">
+        <v>576</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21">
+        <v>169</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21">
+        <v>484</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21">
+        <v>2646</v>
+      </c>
+      <c r="I21">
+        <v>-1.0463799081607126</v>
+      </c>
+      <c r="J21">
+        <v>-0.8845534868295094</v>
+      </c>
+      <c r="K21">
+        <v>3.514557289700363</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>576</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22">
+        <v>169</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22">
+        <v>529</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22">
+        <v>2904</v>
+      </c>
+      <c r="I22">
+        <v>-0.1765369141189771</v>
+      </c>
+      <c r="J22">
+        <v>-0.12649909952638835</v>
+      </c>
+      <c r="K22">
+        <v>3.720177102833961</v>
+      </c>
+    </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
         <v>11</v>
